--- a/Doc/GameExcels/dic_language.xlsx
+++ b/Doc/GameExcels/dic_language.xlsx
@@ -5,18 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WPS office\WPS Office\12.1.0.28043\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Yijue\Shanhaijing_laya\Doc\GameExcels\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView firstSheet="1" activeTab="1"/>
+    <workbookView windowHeight="17775" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#meta" sheetId="2" state="hidden" r:id="rId1"/>
-    <sheet name="data" sheetId="1" r:id="rId2"/>
+    <sheet name="UI" sheetId="1" r:id="rId2"/>
+    <sheet name="mountains" sheetId="3" r:id="rId3"/>
+    <sheet name="seas" sheetId="5" r:id="rId4"/>
+    <sheet name="myths" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UI!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">mountains!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">myths!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">seas!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="57">
   <si>
     <t>rootType</t>
   </si>
@@ -68,13 +74,16 @@
     <t>els</t>
   </si>
   <si>
-    <t>language_select</t>
-  </si>
-  <si>
-    <t>简体中文</t>
-  </si>
-  <si>
-    <t>繁体中文</t>
+    <t>string</t>
+  </si>
+  <si>
+    <t>多语言键值</t>
+  </si>
+  <si>
+    <t>中文简体</t>
+  </si>
+  <si>
+    <t>中文繁体</t>
   </si>
   <si>
     <t>英语</t>
@@ -216,7 +225,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +237,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -377,7 +394,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,6 +409,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA63CD2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -577,12 +606,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -703,76 +747,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -781,10 +819,10 @@
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -793,10 +831,10 @@
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -805,10 +843,10 @@
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -817,10 +855,10 @@
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -829,15 +867,27 @@
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1388,8 +1438,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="17.125" customWidth="1"/>
     <col min="2" max="3" width="12.875" customWidth="1"/>
@@ -1431,161 +1481,631 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:8">
+      <c r="A4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:8">
+      <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" spans="1:8">
+      <c r="A6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:8">
+      <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="15.275" customWidth="1"/>
+    <col min="8" max="8" width="44.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="15.275" customWidth="1"/>
+    <col min="8" max="8" width="44.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="17.125" customWidth="1"/>
+    <col min="2" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="19.375" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="7" max="7" width="15.275" customWidth="1"/>
+    <col min="8" max="8" width="44.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" spans="1:8">
-      <c r="A3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:8">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:8">
-      <c r="A5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>55</v>
-      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H7" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
